--- a/Result/checksun_type/水泥.xlsx
+++ b/Result/checksun_type/水泥.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,22 +1683,22 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>14.91</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>15.77</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>15.38</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>15.77</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2650,7 +2654,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2665,22 +2669,22 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>15.02</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>15.47</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>15.81</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>15.47</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>15.81</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3647,22 +3655,22 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>15.095</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>15.54</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>15.84</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>15.54</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>15.84</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4629,22 +4641,22 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>15.185</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>15.61</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>15.86</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>15.61</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>15.86</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5596,7 +5612,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5611,22 +5627,22 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>15.335</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>15.69</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>15.89</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>15.69</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>15.89</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6578,7 +6598,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6593,22 +6613,22 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>15.46</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>15.92</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>15.75</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>15.92</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7560,7 +7584,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7575,22 +7599,22 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>15.575</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>15.94</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>15.94</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8542,7 +8570,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8557,22 +8585,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>15.67</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>15.85</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>15.95</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>15.85</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>15.95</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9524,7 +9556,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9539,22 +9571,22 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>15.72</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>15.88</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>15.96</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>15.88</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>15.96</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10506,7 +10542,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10521,7 +10557,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>13.34</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>13.53</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>13.39</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>13.53</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11488,7 +11528,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11503,7 +11543,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>13.355</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>13.54</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>13.54</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12470,7 +12514,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -12485,7 +12529,7 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>13.37</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>13.55</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>13.41</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>13.55</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13452,7 +13500,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -13467,7 +13515,7 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>13.375</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>13.42</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>13.56</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>13.42</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>13.56</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14434,7 +14486,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -14449,7 +14501,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>13.38</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>13.57</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>13.43</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>13.57</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15416,7 +15472,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15431,7 +15487,7 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>13.39</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>13.44</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>13.58</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>13.44</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>13.58</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16398,7 +16458,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -16413,7 +16473,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>13.4</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>13.61</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>13.46</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17380,7 +17444,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17395,7 +17459,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>13.415</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>13.47</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>13.63</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>13.47</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>13.63</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18362,7 +18430,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18377,7 +18445,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>13.43</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>13.48</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>13.66</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>13.48</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>13.66</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19344,7 +19416,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -19359,7 +19431,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -19569,11 +19641,15 @@
           <t>11.1</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>11.62</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>11.24</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>11.62</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20326,7 +20402,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -20341,7 +20417,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -20551,11 +20627,15 @@
           <t>11.09</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>11.64</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>11.26</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>11.64</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21308,7 +21388,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -21323,7 +21403,7 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -21533,11 +21613,15 @@
           <t>11.08</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>11.67</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>11.29</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>11.67</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22290,7 +22374,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -22305,7 +22389,7 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -22515,11 +22599,15 @@
           <t>11.075</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>11.69</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>11.32</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>11.69</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23272,7 +23360,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -23287,7 +23375,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -23497,11 +23585,15 @@
           <t>11.095</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>11.36</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>11.71</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>11.36</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>11.71</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24254,7 +24346,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -24269,7 +24361,7 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -24479,11 +24571,15 @@
           <t>11.125</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>11.74</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>11.39</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>11.74</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25236,7 +25332,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -25251,7 +25347,7 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -25461,11 +25557,15 @@
           <t>11.17</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>11.8</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>11.43</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26218,7 +26318,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26233,7 +26333,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -26443,11 +26543,15 @@
           <t>11.22</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>11.84</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>11.46</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27200,7 +27304,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27215,7 +27319,7 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
@@ -27425,11 +27529,15 @@
           <t>11.27</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>11.9</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>11.49</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28182,7 +28290,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -28197,22 +28305,22 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28407,11 +28515,15 @@
           <t>26.685</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>26.97</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>26.8</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>26.97</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29164,7 +29276,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29179,22 +29291,22 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29389,11 +29501,15 @@
           <t>26.695</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>26.8</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>26.99</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30146,7 +30262,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30161,22 +30277,22 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30371,11 +30487,15 @@
           <t>26.69</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>27.01</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>26.8</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>27.01</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31128,7 +31248,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31143,22 +31263,22 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31353,11 +31473,15 @@
           <t>26.705</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>27.01</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>26.8</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>27.01</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32110,7 +32234,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32125,22 +32249,22 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32335,11 +32459,15 @@
           <t>26.77</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>27</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>26.8</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33092,7 +33220,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33107,22 +33235,22 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33317,11 +33445,15 @@
           <t>26.83</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>27</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>26.8</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34074,7 +34206,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34089,22 +34221,22 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34299,11 +34431,15 @@
           <t>26.895</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>27</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>26.81</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>26.81</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35056,7 +35192,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35071,22 +35207,22 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35281,11 +35417,15 @@
           <t>26.98</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>27</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>26.81</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>26.81</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36038,7 +36178,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36053,22 +36193,22 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36263,11 +36403,15 @@
           <t>27.07</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>27.02</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>26.82</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>27.02</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>26.82</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37015,12 +37159,12 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -37035,22 +37179,22 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37245,11 +37389,15 @@
           <t>13.145</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>13.16</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>13.14</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>13.16</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -37997,12 +38145,12 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38017,22 +38165,22 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38227,11 +38375,15 @@
           <t>13.125</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>13.17</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>13.14</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>13.17</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -38979,12 +39131,12 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -38999,22 +39151,22 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39209,11 +39361,15 @@
           <t>13.105</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>13.18</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>13.14</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>13.18</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -39966,7 +40122,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -39981,22 +40137,22 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40191,11 +40347,15 @@
           <t>13.09</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>13.18</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>13.14</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>13.18</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -40948,7 +41108,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -40963,22 +41123,22 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41173,11 +41333,15 @@
           <t>13.095</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>13.2</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>13.15</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -41930,7 +42094,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -41945,22 +42109,22 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42155,11 +42319,15 @@
           <t>13.105</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>13.16</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>13.21</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>13.16</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>13.21</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -42912,7 +43080,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -42927,22 +43095,22 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43137,11 +43305,15 @@
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>13.22</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>13.17</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>13.22</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -43894,7 +44066,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -43909,22 +44081,22 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44119,11 +44291,15 @@
           <t>13.115</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>13.22</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>13.18</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>13.22</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -44871,12 +45047,12 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -44891,22 +45067,22 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45101,11 +45277,15 @@
           <t>13.12</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>13.23</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>13.18</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>13.23</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
@@ -45848,7 +46028,7 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
@@ -45858,37 +46038,37 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -46083,11 +46263,15 @@
           <t>35.515</t>
         </is>
       </c>
-      <c r="CQ47" t="n">
-        <v>35.35</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>34.27</v>
+      <c r="CQ47" t="inlineStr">
+        <is>
+          <t>35.35</t>
+        </is>
+      </c>
+      <c r="CR47" t="inlineStr">
+        <is>
+          <t>34.27</t>
+        </is>
       </c>
       <c r="CS47" t="inlineStr">
         <is>
@@ -46825,12 +47009,12 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
@@ -46840,37 +47024,37 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
@@ -47065,11 +47249,15 @@
           <t>35.45</t>
         </is>
       </c>
-      <c r="CQ48" t="n">
-        <v>35.32</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>34.21</v>
+      <c r="CQ48" t="inlineStr">
+        <is>
+          <t>35.32</t>
+        </is>
+      </c>
+      <c r="CR48" t="inlineStr">
+        <is>
+          <t>34.21</t>
+        </is>
       </c>
       <c r="CS48" t="inlineStr">
         <is>
@@ -47807,12 +47995,12 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
@@ -47822,37 +48010,37 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -48047,11 +48235,15 @@
           <t>35.40499999999999</t>
         </is>
       </c>
-      <c r="CQ49" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="CR49" t="n">
-        <v>34.16</v>
+      <c r="CQ49" t="inlineStr">
+        <is>
+          <t>35.3</t>
+        </is>
+      </c>
+      <c r="CR49" t="inlineStr">
+        <is>
+          <t>34.16</t>
+        </is>
       </c>
       <c r="CS49" t="inlineStr">
         <is>
@@ -48784,17 +48976,17 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
@@ -48804,37 +48996,37 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -49029,11 +49221,15 @@
           <t>35.325</t>
         </is>
       </c>
-      <c r="CQ50" t="n">
-        <v>35.23</v>
-      </c>
-      <c r="CR50" t="n">
-        <v>34.1</v>
+      <c r="CQ50" t="inlineStr">
+        <is>
+          <t>35.23</t>
+        </is>
+      </c>
+      <c r="CR50" t="inlineStr">
+        <is>
+          <t>34.1</t>
+        </is>
       </c>
       <c r="CS50" t="inlineStr">
         <is>
@@ -49766,17 +49962,17 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
@@ -49786,37 +49982,37 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -50011,11 +50207,15 @@
           <t>35.325</t>
         </is>
       </c>
-      <c r="CQ51" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>34.06</v>
+      <c r="CQ51" t="inlineStr">
+        <is>
+          <t>35.2</t>
+        </is>
+      </c>
+      <c r="CR51" t="inlineStr">
+        <is>
+          <t>34.06</t>
+        </is>
       </c>
       <c r="CS51" t="inlineStr">
         <is>
@@ -50743,62 +50943,62 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV52" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -50993,11 +51193,15 @@
           <t>35.3</t>
         </is>
       </c>
-      <c r="CQ52" t="n">
-        <v>35.16</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>34.01</v>
+      <c r="CQ52" t="inlineStr">
+        <is>
+          <t>35.16</t>
+        </is>
+      </c>
+      <c r="CR52" t="inlineStr">
+        <is>
+          <t>34.01</t>
+        </is>
       </c>
       <c r="CS52" t="inlineStr">
         <is>
@@ -51750,37 +51954,37 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -51975,11 +52179,15 @@
           <t>35.245</t>
         </is>
       </c>
-      <c r="CQ53" t="n">
-        <v>35.13</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>33.98</v>
+      <c r="CQ53" t="inlineStr">
+        <is>
+          <t>35.13</t>
+        </is>
+      </c>
+      <c r="CR53" t="inlineStr">
+        <is>
+          <t>33.98</t>
+        </is>
       </c>
       <c r="CS53" t="inlineStr">
         <is>
@@ -52732,37 +52940,37 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -52957,11 +53165,15 @@
           <t>35.22</t>
         </is>
       </c>
-      <c r="CQ54" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>33.96</v>
+      <c r="CQ54" t="inlineStr">
+        <is>
+          <t>35.1</t>
+        </is>
+      </c>
+      <c r="CR54" t="inlineStr">
+        <is>
+          <t>33.96</t>
+        </is>
       </c>
       <c r="CS54" t="inlineStr">
         <is>
@@ -53714,7 +53926,7 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -53729,22 +53941,22 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
@@ -53939,11 +54151,15 @@
           <t>35.2</t>
         </is>
       </c>
-      <c r="CQ55" t="n">
-        <v>35.08</v>
-      </c>
-      <c r="CR55" t="n">
-        <v>33.95</v>
+      <c r="CQ55" t="inlineStr">
+        <is>
+          <t>35.08</t>
+        </is>
+      </c>
+      <c r="CR55" t="inlineStr">
+        <is>
+          <t>33.95</t>
+        </is>
       </c>
       <c r="CS55" t="inlineStr">
         <is>
@@ -54676,34 +54892,34 @@
       </c>
       <c r="AR56" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV56" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AX56" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -54711,22 +54927,22 @@
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
@@ -54921,11 +55137,15 @@
           <t>25.09</t>
         </is>
       </c>
-      <c r="CQ56" t="n">
-        <v>24.72</v>
-      </c>
-      <c r="CR56" t="n">
-        <v>24.49</v>
+      <c r="CQ56" t="inlineStr">
+        <is>
+          <t>24.72</t>
+        </is>
+      </c>
+      <c r="CR56" t="inlineStr">
+        <is>
+          <t>24.49</t>
+        </is>
       </c>
       <c r="CS56" t="inlineStr">
         <is>
@@ -55041,7 +55261,7 @@
       </c>
       <c r="DQ56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR56" t="inlineStr">
@@ -55653,62 +55873,62 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -55903,11 +56123,15 @@
           <t>24.96</t>
         </is>
       </c>
-      <c r="CQ57" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="CR57" t="n">
-        <v>24.46</v>
+      <c r="CQ57" t="inlineStr">
+        <is>
+          <t>24.69</t>
+        </is>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>24.46</t>
+        </is>
       </c>
       <c r="CS57" t="inlineStr">
         <is>
@@ -56023,7 +56247,7 @@
       </c>
       <c r="DQ57" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR57" t="inlineStr">
@@ -56640,17 +56864,17 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
@@ -56660,37 +56884,37 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW58" t="inlineStr">
+      <c r="AX58" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
+      <c r="AY58" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -56885,11 +57109,15 @@
           <t>24.785</t>
         </is>
       </c>
-      <c r="CQ58" t="n">
-        <v>24.68</v>
-      </c>
-      <c r="CR58" t="n">
-        <v>24.43</v>
+      <c r="CQ58" t="inlineStr">
+        <is>
+          <t>24.68</t>
+        </is>
+      </c>
+      <c r="CR58" t="inlineStr">
+        <is>
+          <t>24.43</t>
+        </is>
       </c>
       <c r="CS58" t="inlineStr">
         <is>
@@ -57005,7 +57233,7 @@
       </c>
       <c r="DQ58" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR58" t="inlineStr">
@@ -57617,22 +57845,22 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
@@ -57642,37 +57870,37 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW59" t="inlineStr">
+      <c r="AX59" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
+      <c r="AY59" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
@@ -57867,11 +58095,15 @@
           <t>24.545</t>
         </is>
       </c>
-      <c r="CQ59" t="n">
-        <v>24.58</v>
-      </c>
-      <c r="CR59" t="n">
-        <v>24.38</v>
+      <c r="CQ59" t="inlineStr">
+        <is>
+          <t>24.58</t>
+        </is>
+      </c>
+      <c r="CR59" t="inlineStr">
+        <is>
+          <t>24.38</t>
+        </is>
       </c>
       <c r="CS59" t="inlineStr">
         <is>
@@ -57987,7 +58219,7 @@
       </c>
       <c r="DQ59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR59" t="inlineStr">
@@ -58599,22 +58831,22 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
@@ -58624,37 +58856,37 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW60" t="inlineStr">
+      <c r="AX60" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
+      <c r="AY60" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
@@ -58849,11 +59081,15 @@
           <t>24.465</t>
         </is>
       </c>
-      <c r="CQ60" t="n">
-        <v>24.53</v>
-      </c>
-      <c r="CR60" t="n">
-        <v>24.35</v>
+      <c r="CQ60" t="inlineStr">
+        <is>
+          <t>24.53</t>
+        </is>
+      </c>
+      <c r="CR60" t="inlineStr">
+        <is>
+          <t>24.35</t>
+        </is>
       </c>
       <c r="CS60" t="inlineStr">
         <is>
@@ -58969,7 +59205,7 @@
       </c>
       <c r="DQ60" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR60" t="inlineStr">
@@ -59581,22 +59817,22 @@
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
@@ -59606,37 +59842,37 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW61" t="inlineStr">
+      <c r="AX61" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
+      <c r="AY61" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
@@ -59831,11 +60067,15 @@
           <t>24.42</t>
         </is>
       </c>
-      <c r="CQ61" t="n">
-        <v>24.48</v>
-      </c>
-      <c r="CR61" t="n">
-        <v>24.32</v>
+      <c r="CQ61" t="inlineStr">
+        <is>
+          <t>24.48</t>
+        </is>
+      </c>
+      <c r="CR61" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
       </c>
       <c r="CS61" t="inlineStr">
         <is>
@@ -59951,7 +60191,7 @@
       </c>
       <c r="DQ61" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR61" t="inlineStr">
@@ -60578,17 +60818,17 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
@@ -60598,27 +60838,27 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
@@ -60813,11 +61053,15 @@
           <t>24.33</t>
         </is>
       </c>
-      <c r="CQ62" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="CR62" t="n">
-        <v>24.28</v>
+      <c r="CQ62" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="CR62" t="inlineStr">
+        <is>
+          <t>24.28</t>
+        </is>
       </c>
       <c r="CS62" t="inlineStr">
         <is>
@@ -61560,7 +61804,7 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
@@ -61570,7 +61814,7 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
@@ -61580,27 +61824,27 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
@@ -61795,11 +62039,15 @@
           <t>24.305</t>
         </is>
       </c>
-      <c r="CQ63" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>24.24</v>
+      <c r="CQ63" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="CR63" t="inlineStr">
+        <is>
+          <t>24.24</t>
+        </is>
       </c>
       <c r="CS63" t="inlineStr">
         <is>
@@ -62542,7 +62790,7 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
@@ -62552,7 +62800,7 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
@@ -62562,27 +62810,27 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
@@ -62777,11 +63025,15 @@
           <t>24.32</t>
         </is>
       </c>
-      <c r="CQ64" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>24.22</v>
+      <c r="CQ64" t="inlineStr">
+        <is>
+          <t>24.44</t>
+        </is>
+      </c>
+      <c r="CR64" t="inlineStr">
+        <is>
+          <t>24.22</t>
+        </is>
       </c>
       <c r="CS64" t="inlineStr">
         <is>
